--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Procedure: Radiology, ResourceType Procedure</t>
+    <t>This StructureDefinition contains the maps for VistA EXAMINATIONS (file 70.03) to FHIR Procedure</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -249,10 +249,10 @@
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -617,10 +617,10 @@
     <t>FiveWs.status</t>
   </si>
   <si>
+    <t>1506: source value from EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (#70.03-3 &gt; 72-.01)</t>
+  </si>
+  <si>
     <t>Dim.RadiologyExamStatus.RadiologyExamStatus</t>
-  </si>
-  <si>
-    <t>1506: source value from EXAMINATIONS - EXAM STATUS &gt; EXAMINATION STATUS - STATUS (#70.03-3 &gt; 72-.01)</t>
   </si>
   <si>
     <t>Procedure.statusReason</t>
@@ -748,12 +748,12 @@
     <t>C*E.9. But note many systems use C*E.2 for this</t>
   </si>
   <si>
+    <t>1507: source value from EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (#70.03-3.5 &gt; 75.2-.01)</t>
+  </si>
+  <si>
     <t>Dim.RadiologyHoldCancelReason.RadiologyHoldCancelReason</t>
   </si>
   <si>
-    <t>1507: source value from EXAMINATIONS - REASON FOR CANCELLATION &gt; RAD/NUC MED REASON - REASON (#70.03-3.5 &gt; 75.2-.01)</t>
-  </si>
-  <si>
     <t>Procedure.category</t>
   </si>
   <si>
@@ -787,10 +787,10 @@
     <t>Procedure.category.text</t>
   </si>
   <si>
+    <t>1508: source value from REGISTERED EXAMS - TYPE OF IMAGING &gt; IMAGING TYPE - TYPE OF IMAGING (#70.02-2 &gt; 79.2-.01)</t>
+  </si>
+  <si>
     <t>Dim.ImagingType.ImagingType</t>
-  </si>
-  <si>
-    <t>1508: source value from REGISTERED EXAMS - TYPE OF IMAGING &gt; IMAGING TYPE - TYPE OF IMAGING (#70.02-2 &gt; 79.2-.01)</t>
   </si>
   <si>
     <t>Procedure.code</t>
@@ -948,6 +948,9 @@
   <si>
     <t xml:space="preserve">dateTime
 </t>
+  </si>
+  <si>
+    <t>1512: source value from REGISTERED EXAMS - EXAM DATE (#70.02-.01)</t>
   </si>
   <si>
     <t>Rad.RadiologyExam.ExamDateTime
@@ -959,9 +962,6 @@
 Rad.RadiologyExamStatusList.ExamDateTime
 Rad.RadiologyExamTechnologist.ExamDateTime
 Rad.RadiologyRegisteredExam.ExamDateTime</t>
-  </si>
-  <si>
-    <t>1512: source value from REGISTERED EXAMS - EXAM DATE (#70.02-.01)</t>
   </si>
   <si>
     <t>Procedure.recorder</t>
@@ -1782,8 +1782,8 @@
     <col min="38" max="38" width="142.56640625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="105.16015625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="58.35546875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="123.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="123.1640625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="58.35546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5386,10 +5386,10 @@
         <v>225</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>79</v>
+        <v>264</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>264</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" hidden="true">
@@ -5626,10 +5626,10 @@
         <v>274</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>79</v>
+        <v>275</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>275</v>
+        <v>79</v>
       </c>
     </row>
     <row r="33" hidden="true">
@@ -5746,10 +5746,10 @@
         <v>284</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>285</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" hidden="true">
@@ -6940,10 +6940,10 @@
         <v>342</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>343</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" hidden="true">
@@ -7180,10 +7180,10 @@
         <v>79</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>79</v>
+        <v>357</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>357</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" hidden="true">

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
+++ b/docs/StructureDefinition-ProcedureRadiologyProcedure.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA EXAMINATIONS (file 70.03) to FHIR Procedure</t>
+    <t>This StructureDefinition contains the maps for VistA file EXAMINATIONS (#70.03) to us-core-procedure</t>
   </si>
   <si>
     <t>Purpose</t>
